--- a/backend/templates/reportes/Ficha SIGUD audiovisuales.xlsx
+++ b/backend/templates/reportes/Ficha SIGUD audiovisuales.xlsx
@@ -1,16 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70EE91B9-77E1-48C6-B220-F86E5CF03B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9758C514-3BC7-408F-B77D-7DD3EC83DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28560" windowHeight="13905" firstSheet="1" activeTab="1" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{A22C7B05-6B0A-4116-A99A-60EDDEA67682}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Ficha - SIGUD Audiovisuales" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Ficha - SIGUD Audiovisuales'!$A$1:$G$22</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>SOLICITUD PRÉSTAMO AUDIOVISUALES</t>
   </si>
@@ -110,9 +113,6 @@
   </si>
   <si>
     <t xml:space="preserve">Observaciones: </t>
-  </si>
-  <si>
-    <t>Se prestó Cable HDMI. Se prestó Extensión. Atendido por:</t>
   </si>
   <si>
     <t>Firma</t>
@@ -122,7 +122,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,9 +131,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="7"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -141,21 +141,21 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="2" tint="-9.9978637043366805E-2"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -349,64 +349,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -415,49 +416,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,15 +483,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>85725</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>45027</xdr:rowOff>
+      <xdr:rowOff>6927</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>389660</xdr:colOff>
+      <xdr:colOff>380135</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>183572</xdr:rowOff>
+      <xdr:rowOff>145472</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -505,7 +506,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1828800" y="2397702"/>
+          <a:off x="1819275" y="2359602"/>
           <a:ext cx="294410" cy="138545"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -641,15 +642,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>497032</xdr:colOff>
+      <xdr:colOff>649432</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>54262</xdr:rowOff>
+      <xdr:rowOff>6637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>791442</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>2307</xdr:rowOff>
+      <xdr:colOff>943842</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>145182</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -667,7 +668,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3773632" y="2406937"/>
+          <a:off x="3926032" y="2359312"/>
           <a:ext cx="294410" cy="138545"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -793,15 +794,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>445076</xdr:colOff>
+      <xdr:colOff>673676</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>53109</xdr:rowOff>
+      <xdr:rowOff>5484</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>739486</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1154</xdr:rowOff>
+      <xdr:colOff>968086</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>144029</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -819,7 +820,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5045651" y="2405784"/>
+          <a:off x="5274251" y="2358159"/>
           <a:ext cx="294410" cy="138545"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1040,9 +1041,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1080,7 +1081,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1186,7 +1187,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1328,7 +1329,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1337,7 +1338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F274FABB-DF5C-4F9E-B98F-F8DC866DADF5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1347,7 +1348,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A16F3E-296C-4C8D-BF78-2B876D2CC67D}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
@@ -1358,60 +1359,66 @@
     <col min="7" max="7" width="3.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="5.25" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" ht="25.5">
-      <c r="A2" s="1"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="27" t="s">
+    <row r="1" spans="1:7" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="29" t="s">
+      <c r="F2" s="25"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="31"/>
+      <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="34.5" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="31" t="s">
+      <c r="F3" s="26"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="10" t="s">
         <v>6</v>
       </c>
@@ -1424,62 +1431,67 @@
       <c r="F6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
       <c r="B8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="13"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
       <c r="B9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
       <c r="B10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
       <c r="B11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
       <c r="B12" s="12" t="s">
         <v>16</v>
       </c>
@@ -1493,116 +1505,114 @@
       <c r="F12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
       <c r="B13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
       <c r="B14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
       <c r="B15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1"/>
-      <c r="B17" s="33" t="s">
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="6.75" customHeight="1">
-      <c r="A20" s="1"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
       <c r="B21" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" ht="6" customHeight="1">
-      <c r="A22" s="3"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+        <v>24</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="22"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1622,8 +1632,9 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
-  <pageMargins left="4.6296296296296294E-2" right="0.25" top="5.7870370370370371E-2" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="119" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="160" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>